--- a/dados/excel/genero_por_secretaria.xlsx
+++ b/dados/excel/genero_por_secretaria.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$H$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$H$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -646,7 +646,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -892,22 +892,22 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="D2" s="10" t="n">
         <v>169</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>8935258.59</v>
+        <v>8948253.720000001</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4061.481177272727</v>
+        <v>4065.540081781009</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H2" s="13" t="n">
-        <v>86.22</v>
+        <v>85.79000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>4328494.06</v>
+        <v>4481023.14</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>14722.76891156462</v>
+        <v>14788.85524752475</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>86.22</v>
+        <v>85.79000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -964,10 +964,10 @@
         <v>3868.411785714286</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>86.22</v>
+        <v>85.79000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>8187</v>
+        <v>8317</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>205</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>35952180.48</v>
+        <v>36680963.84</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>4391.374188347379</v>
+        <v>4410.359966334016</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>297</v>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>2952</v>
+        <v>2996</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>88</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>17511963.66</v>
+        <v>17836386.96</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>5932.237012195122</v>
+        <v>5953.400186915888</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>297</v>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>974168.66</v>
+        <v>994740.0599999999</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>6538.044697986577</v>
+        <v>6587.682516556291</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>297</v>
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>13635</v>
+        <v>13887</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>96647619.89</v>
+        <v>98828527.94</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>7088.200945361203</v>
+        <v>7116.621872254626</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>69.36</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="9">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>4773</v>
+        <v>4855</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>36641513.34</v>
+        <v>37422399.13</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>7676.830785669391</v>
+        <v>7708.012179196705</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>69.36</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="10">
@@ -1132,22 +1132,22 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>3</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>979498.4399999999</v>
+        <v>1007020.49</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>6946.79744680851</v>
+        <v>6993.197847222222</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>69.36</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="11">
@@ -1162,22 +1162,22 @@
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>438434</v>
+        <v>446428</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>15633</v>
+        <v>15944</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>2402318822.22</v>
+        <v>2458493083.55</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>5479.316891983742</v>
+        <v>5507.031556152392</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>17452</v>
+        <v>17797</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>89.58</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="12">
@@ -1192,22 +1192,22 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>45379</v>
+        <v>46152</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1630</v>
+        <v>1661</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>244044462.5</v>
+        <v>249775420.3</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>5377.916271843805</v>
+        <v>5412.017253856821</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>17452</v>
+        <v>17797</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>89.58</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="13">
@@ -1222,22 +1222,22 @@
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>5905</v>
+        <v>6005</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>32196499.22</v>
+        <v>32947751.44</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>5452.413077053345</v>
+        <v>5486.719640299751</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>17452</v>
+        <v>17797</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>89.58</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="14">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>7158</v>
+        <v>7258</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>181</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>50454419.81</v>
+        <v>51677735.24</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7048.675581167924</v>
+        <v>7120.106811793883</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>304</v>
@@ -1282,16 +1282,16 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>5417</v>
+        <v>5492</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>117</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>56012864.83</v>
+        <v>57158003.44</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>10340.20026398375</v>
+        <v>10407.50244719592</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>304</v>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>6</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3284838.64</v>
+        <v>3373786.36</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12781.473307393</v>
+        <v>12926.3845210728</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>304</v>
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>47</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>10019730.4</v>
+        <v>10235511.1</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>9303.370844939647</v>
+        <v>9321.959107468123</v>
       </c>
       <c r="G17" s="18" t="n">
         <v>93</v>
@@ -1372,16 +1372,16 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1556</v>
+        <v>1579</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>46</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>11451574.71</v>
+        <v>11710927.11</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7359.623849614396</v>
+        <v>7416.673280557315</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>93</v>
@@ -1402,52 +1402,52 @@
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>3614991.77</v>
+        <v>3791668.94</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>15785.99026200873</v>
+        <v>15413.28837398374</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>124186</v>
+        <v>1</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2636</v>
+        <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1040285394.44</v>
+        <v>482.56</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8376.833092619136</v>
+        <v>482.56</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>3963</v>
+        <v>24</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>66.52</v>
+        <v>95.83</v>
       </c>
     </row>
     <row r="21">
@@ -1458,26 +1458,26 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>55083</v>
+        <v>126373</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1266</v>
+        <v>2644</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>627433009.3099999</v>
+        <v>1062531888.05</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>11390.68331989906</v>
+        <v>8407.902701130779</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>3963</v>
+        <v>3977</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>66.52</v>
+        <v>66.48</v>
       </c>
     </row>
     <row r="22">
@@ -1488,56 +1488,56 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>3195</v>
+        <v>56089</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>61</v>
+        <v>1272</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>34434281.9</v>
+        <v>639677396.27</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10777.55302034429</v>
+        <v>11404.68534418513</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3963</v>
+        <v>3977</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>66.52</v>
+        <v>66.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>8891</v>
+        <v>3238</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>318</v>
+        <v>61</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>60411091.77</v>
+        <v>34916377.44</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>6794.634098526601</v>
+        <v>10783.31607164917</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>585</v>
+        <v>3977</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>44.27</v>
+        <v>66.48</v>
       </c>
     </row>
     <row r="24">
@@ -1548,20 +1548,20 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>7011</v>
+        <v>8972</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>49715129.91</v>
+        <v>61217402.78</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7091.01838682071</v>
+        <v>6823.161255015604</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>585</v>
@@ -1578,20 +1578,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>325</v>
+        <v>7093</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>1663713.57</v>
+        <v>50510458.56</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>5119.118676923077</v>
+        <v>7121.169964753984</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>585</v>
@@ -1603,31 +1603,31 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>5060</v>
+        <v>328</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>61397076.12</v>
+        <v>1679175.13</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>12133.80950988142</v>
+        <v>5119.43637195122</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>293</v>
+        <v>585</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>56.66</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="27">
@@ -1638,26 +1638,26 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>3774</v>
+        <v>5135</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>65043545.77</v>
+        <v>62625762.01</v>
       </c>
       <c r="F27" s="17" t="n">
-        <v>17234.64381823</v>
+        <v>12195.86407205453</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>56.66</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="28">
@@ -1668,56 +1668,56 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>105</v>
+        <v>3845</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>536935.8099999999</v>
+        <v>66432235.11</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5113.67438095238</v>
+        <v>17277.56439791938</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>56.66</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>1223</v>
+        <v>106</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>9917646.439999999</v>
+        <v>541358.15</v>
       </c>
       <c r="F29" s="17" t="n">
-        <v>8109.277547015535</v>
+        <v>5107.152358490566</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>86</v>
+        <v>298</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>53.49</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="30">
@@ -1728,26 +1728,26 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>861</v>
+        <v>1242</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>9804654.82</v>
+        <v>10110147.98</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>11387.52011614402</v>
+        <v>8140.215764895331</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>53.49</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="31">
@@ -1758,56 +1758,56 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>2</v>
+        <v>878</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>42051.55</v>
+        <v>10013491.53</v>
       </c>
       <c r="F31" s="17" t="n">
-        <v>21025.775</v>
+        <v>11404.88784738041</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>53.49</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2154</v>
+        <v>2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>11582162.47</v>
+        <v>42051.55</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5377.048500464253</v>
+        <v>21025.775</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>205</v>
+        <v>87</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>51.71</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="33">
@@ -1818,26 +1818,26 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>2405</v>
+        <v>2193</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>15304511.49</v>
+        <v>11870186.5</v>
       </c>
       <c r="F33" s="17" t="n">
-        <v>6363.622241164241</v>
+        <v>5412.761741906064</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>51.71</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="34">
@@ -1848,56 +1848,56 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>72</v>
+        <v>2444</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>973161.02</v>
+        <v>15587279.17</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>13516.12527777778</v>
+        <v>6377.773801145663</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>51.71</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>1884</v>
+        <v>74</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>13972657.26</v>
+        <v>990610.48</v>
       </c>
       <c r="F35" s="17" t="n">
-        <v>7416.48474522293</v>
+        <v>13386.62810810811</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>45.02</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="36">
@@ -1908,20 +1908,20 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>2272</v>
+        <v>1893</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>14385544.85</v>
+        <v>14054657.37</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6331.665867077465</v>
+        <v>7424.541664025356</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>251</v>
@@ -1938,20 +1938,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>91</v>
+        <v>2283</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>495568.28</v>
+        <v>14525232.8</v>
       </c>
       <c r="F37" s="17" t="n">
-        <v>5445.805274725274</v>
+        <v>6362.344634253176</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>251</v>
@@ -1963,31 +1963,31 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>368</v>
+        <v>91</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>3104635.38</v>
+        <v>495568.28</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>8436.509184782608</v>
+        <v>5445.805274725274</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>42</v>
+        <v>251</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>57.14</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="39">
@@ -1998,20 +1998,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>149</v>
+        <v>390</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>1774208.39</v>
+        <v>3293633.81</v>
       </c>
       <c r="F39" s="17" t="n">
-        <v>11907.4388590604</v>
+        <v>8445.214897435897</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>42</v>
@@ -2023,7 +2023,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -2032,22 +2032,22 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>4287</v>
+        <v>161</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>39033530.09</v>
+        <v>1900201.46</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>9105.092160018661</v>
+        <v>11802.49354037267</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>206</v>
+        <v>42</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>31.07</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="41">
@@ -2058,26 +2058,26 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>1506</v>
+        <v>4357</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>10566916.73</v>
+        <v>39921827.76</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>7016.544973439575</v>
+        <v>9162.687114987377</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>31.07</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="42">
@@ -2088,56 +2088,56 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>80</v>
+        <v>1540</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>582366.74</v>
+        <v>10831492.68</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>7279.58425</v>
+        <v>7033.436805194805</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>31.07</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>3151</v>
+        <v>81</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>34556041.3</v>
+        <v>595161.4299999999</v>
       </c>
       <c r="F43" s="17" t="n">
-        <v>10966.69035226912</v>
+        <v>7347.671975308641</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>329</v>
+        <v>207</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>46.5</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="44">
@@ -2148,26 +2148,26 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>3528</v>
+        <v>3257</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>31137363.1</v>
+        <v>35649982.13</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>8825.783191609979</v>
+        <v>10945.65002456248</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>46.5</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="45">
@@ -2178,56 +2178,56 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>33</v>
+        <v>3601</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>579872.61</v>
+        <v>31856368.14</v>
       </c>
       <c r="F45" s="17" t="n">
-        <v>17571.89727272727</v>
+        <v>8846.533779505693</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>46.5</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>4489</v>
+        <v>33</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>303</v>
+        <v>3</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>46080409.61</v>
+        <v>579872.61</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10265.1836957006</v>
+        <v>17571.89727272727</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>506</v>
+        <v>341</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>59.88</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="47">
@@ -2238,26 +2238,26 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>3005</v>
+        <v>4565</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>194</v>
+        <v>308</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>30383952.21</v>
+        <v>47040298.18</v>
       </c>
       <c r="F47" s="17" t="n">
-        <v>10111.13218302829</v>
+        <v>10304.55600876232</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>59.88</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="48">
@@ -2268,56 +2268,56 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>53</v>
+        <v>3060</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>9</v>
+        <v>198</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>315577.87</v>
+        <v>31097873.32</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5954.299433962264</v>
+        <v>10162.70369934641</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>59.88</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>1767947.37</v>
+        <v>337923.81</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>11631.23269736842</v>
+        <v>5928.487894736842</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>19</v>
+        <v>515</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>57.89</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="50">
@@ -2328,20 +2328,20 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1288718.49</v>
+        <v>1873242.76</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>13150.18867346939</v>
+        <v>11707.76725</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>19</v>
@@ -2353,7 +2353,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
@@ -2362,22 +2362,22 @@
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>1512</v>
+        <v>104</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>15239854.17</v>
+        <v>1349367.99</v>
       </c>
       <c r="F51" s="17" t="n">
-        <v>10079.26863095238</v>
+        <v>12974.69221153846</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>32.61</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="52">
@@ -2388,26 +2388,26 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>785</v>
+        <v>1565</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>4167939.53</v>
+        <v>15710543.51</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5309.477108280254</v>
+        <v>10038.68594888179</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>32.61</v>
+        <v>32.37</v>
       </c>
     </row>
     <row r="53">
@@ -2418,56 +2418,56 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>24</v>
+        <v>807</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>26111.84</v>
+        <v>4294701.87</v>
       </c>
       <c r="F53" s="17" t="n">
-        <v>1087.993333333333</v>
+        <v>5321.811486988848</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>32.61</v>
+        <v>32.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>659</v>
+        <v>24</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>5935214.67</v>
+        <v>26111.84</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>9006.395553869499</v>
+        <v>1087.993333333333</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>54.43</v>
+        <v>32.37</v>
       </c>
     </row>
     <row r="55">
@@ -2478,32 +2478,32 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C55" s="16" t="n">
-        <v>532</v>
+        <v>692</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E55" s="17" t="n">
-        <v>5142849.14</v>
+        <v>6325963.71</v>
       </c>
       <c r="F55" s="17" t="n">
-        <v>9667.009661654134</v>
+        <v>9141.566054913295</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>54.43</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -2512,22 +2512,22 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>5839</v>
+        <v>561</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>52696432.6</v>
+        <v>5452504.53</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>9024.907107381401</v>
+        <v>9719.259411764706</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>49.33</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="57">
@@ -2538,26 +2538,26 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C57" s="16" t="n">
-        <v>4488</v>
+        <v>5948</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>26064347.83</v>
+        <v>53849287.84</v>
       </c>
       <c r="F57" s="17" t="n">
-        <v>5807.564133244206</v>
+        <v>9053.343618022865</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>49.33</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="58">
@@ -2568,56 +2568,56 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>18</v>
+        <v>4572</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>187461.08</v>
+        <v>26736591.65</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>10414.50444444444</v>
+        <v>5847.898436132983</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>49.33</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C59" s="16" t="n">
-        <v>5460</v>
+        <v>20</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>197</v>
+        <v>4</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>36740214.64</v>
+        <v>203793.23</v>
       </c>
       <c r="F59" s="17" t="n">
-        <v>6728.977040293041</v>
+        <v>10189.6615</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>290</v>
+        <v>379</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>67.93000000000001</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="60">
@@ -2628,26 +2628,26 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>2700</v>
+        <v>5555</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>22127202.46</v>
+        <v>37597381.4</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>8195.260170370371</v>
+        <v>6768.205472547254</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>67.93000000000001</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="61">
@@ -2658,56 +2658,56 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C61" s="16" t="n">
-        <v>191</v>
+        <v>2741</v>
       </c>
       <c r="D61" s="16" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>1441005.87</v>
+        <v>22561227.29</v>
       </c>
       <c r="F61" s="17" t="n">
-        <v>7544.533350785341</v>
+        <v>8231.020536300621</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>67.93000000000001</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>431</v>
+        <v>194</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>5591529</v>
+        <v>1471893.88</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>12973.38515081206</v>
+        <v>7587.081855670102</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>44</v>
+        <v>291</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>27.27</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="63">
@@ -2718,26 +2718,26 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C63" s="16" t="n">
-        <v>359</v>
+        <v>434</v>
       </c>
       <c r="D63" s="16" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>3685952.53</v>
+        <v>5693328.15</v>
       </c>
       <c r="F63" s="17" t="n">
-        <v>10267.27724233983</v>
+        <v>13118.26762672811</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>27.27</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="64">
@@ -2748,56 +2748,56 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>3</v>
+        <v>364</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>47372.72</v>
+        <v>3758970.01</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>15790.90666666667</v>
+        <v>10326.84068681319</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>27.27</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C65" s="16" t="n">
-        <v>745</v>
+        <v>3</v>
       </c>
       <c r="D65" s="16" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>6051379.54</v>
+        <v>47372.72</v>
       </c>
       <c r="F65" s="17" t="n">
-        <v>8122.657100671141</v>
+        <v>15790.90666666667</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>46.9</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="66">
@@ -2808,26 +2808,26 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>968</v>
+        <v>763</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>5447735.81</v>
+        <v>6266632.72</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>5627.826249999999</v>
+        <v>8213.149043250327</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>46.9</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="67">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C67" s="16" t="n">
-        <v>57</v>
+        <v>985</v>
       </c>
       <c r="D67" s="16" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="E67" s="17" t="n">
-        <v>343729.84</v>
+        <v>5549209.77</v>
       </c>
       <c r="F67" s="17" t="n">
-        <v>6030.348070175438</v>
+        <v>5633.715502538071</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>46.9</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>23277</v>
+        <v>59</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>611</v>
+        <v>3</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>235267425.15</v>
+        <v>358104.96</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>10107.2915388581</v>
+        <v>6069.575593220339</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>803</v>
+        <v>114</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>22.79</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="69">
@@ -2898,20 +2898,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C69" s="16" t="n">
-        <v>4475</v>
+        <v>23761</v>
       </c>
       <c r="D69" s="16" t="n">
-        <v>183</v>
+        <v>611</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>38111863.64</v>
+        <v>240518340.12</v>
       </c>
       <c r="F69" s="17" t="n">
-        <v>8516.617573184358</v>
+        <v>10122.39973570136</v>
       </c>
       <c r="G69" s="18" t="n">
         <v>803</v>
@@ -2928,20 +2928,20 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>254</v>
+        <v>4595</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2151508.18</v>
+        <v>39060888.8</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>8470.504645669293</v>
+        <v>8500.737497279652</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>803</v>
@@ -2953,31 +2953,31 @@
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C71" s="16" t="n">
-        <v>7157</v>
+        <v>261</v>
       </c>
       <c r="D71" s="16" t="n">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>57548631.93</v>
+        <v>2217597.71</v>
       </c>
       <c r="F71" s="17" t="n">
-        <v>8040.88751292441</v>
+        <v>8496.542950191571</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>275</v>
+        <v>803</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>26.91</v>
+        <v>22.79</v>
       </c>
     </row>
     <row r="72">
@@ -2988,26 +2988,26 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>2605</v>
+        <v>7274</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>18143208.47</v>
+        <v>58719192.8</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>6964.763328214971</v>
+        <v>8072.476326642837</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>26.91</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="73">
@@ -3018,56 +3018,56 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>169</v>
+        <v>2650</v>
       </c>
       <c r="D73" s="16" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="E73" s="17" t="n">
-        <v>945727.92</v>
+        <v>18545590.13</v>
       </c>
       <c r="F73" s="17" t="n">
-        <v>5596.023195266273</v>
+        <v>6998.335898113207</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>26.91</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>1423906.53</v>
+        <v>986194.28</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>10098.62787234043</v>
+        <v>5767.218011695906</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>30</v>
+        <v>278</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>50</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="75">
@@ -3078,20 +3078,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C75" s="16" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D75" s="16" t="n">
         <v>15</v>
       </c>
       <c r="E75" s="17" t="n">
-        <v>1682063.76</v>
+        <v>1489334.32</v>
       </c>
       <c r="F75" s="17" t="n">
-        <v>10993.88078431373</v>
+        <v>9995.532348993289</v>
       </c>
       <c r="G75" s="18" t="n">
         <v>30</v>
@@ -3103,7 +3103,7 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Urbanismo e Licenciamento</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -3112,22 +3112,22 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>1442</v>
+        <v>161</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>10970178.09</v>
+        <v>1779487.06</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>7607.613099861303</v>
+        <v>11052.71465838509</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>228</v>
+        <v>30</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>42.54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
@@ -3138,20 +3138,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="C77" s="16" t="n">
-        <v>1019</v>
+        <v>1442</v>
       </c>
       <c r="D77" s="16" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>4640863.34</v>
+        <v>10970178.09</v>
       </c>
       <c r="F77" s="17" t="n">
-        <v>4554.331050049068</v>
+        <v>7607.613099861303</v>
       </c>
       <c r="G77" s="18" t="n">
         <v>228</v>
@@ -3168,20 +3168,20 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>indefinido</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>2</v>
+        <v>1019</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>9000.540000000001</v>
+        <v>4640863.34</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>4500.27</v>
+        <v>4554.331050049068</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>228</v>
@@ -3193,31 +3193,31 @@
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Urbanismo e Licenciamento</t>
         </is>
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>feminino</t>
+          <t>indefinido</t>
         </is>
       </c>
       <c r="C79" s="16" t="n">
-        <v>3333</v>
+        <v>2</v>
       </c>
       <c r="D79" s="16" t="n">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>20973298.56</v>
+        <v>9000.540000000001</v>
       </c>
       <c r="F79" s="17" t="n">
-        <v>6292.618829882987</v>
+        <v>4500.27</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>334</v>
+        <v>228</v>
       </c>
       <c r="H79" s="19" t="n">
-        <v>50</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="80">
@@ -3228,26 +3228,26 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>feminino</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>4355</v>
+        <v>3421</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>39140493.8</v>
+        <v>21601666.19</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>8987.484225028702</v>
+        <v>6314.430339082141</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>50</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="81">
@@ -3258,30 +3258,60 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
+          <t>masculino</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>4431</v>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>161</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>39892325.68</v>
+      </c>
+      <c r="F81" s="17" t="n">
+        <v>9003.007375310313</v>
+      </c>
+      <c r="G81" s="18" t="n">
+        <v>338</v>
+      </c>
+      <c r="H81" s="19" t="n">
+        <v>50.59</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
           <t>indefinido</t>
         </is>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D81" s="16" t="n">
+      <c r="C82" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="D82" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="E81" s="17" t="n">
-        <v>665107.11</v>
-      </c>
-      <c r="F81" s="17" t="n">
-        <v>6651.0711</v>
-      </c>
-      <c r="G81" s="18" t="n">
-        <v>334</v>
-      </c>
-      <c r="H81" s="19" t="n">
-        <v>50</v>
+      <c r="E82" s="11" t="n">
+        <v>672919.3</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>6662.567326732674</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>338</v>
+      </c>
+      <c r="H82" s="13" t="n">
+        <v>50.59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H81"/>
+  <autoFilter ref="A1:H82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>